--- a/Convert_from_xlsx_to_Json/table_normalization/education-table06.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/education-table06.xlsx
@@ -241,7 +241,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,12 +251,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,44 +452,44 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -1075,26 +1069,26 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="35" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
     </row>
     <row r="2" spans="1:17" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -1312,52 +1306,52 @@
       <c r="A6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="39">
+      <c r="B6" s="30">
         <v>788560</v>
       </c>
-      <c r="C6" s="39">
+      <c r="C6" s="30">
         <v>44410</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="30">
         <v>29360</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="30">
         <v>239470</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="30">
         <v>1120</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="30">
         <v>352220</v>
       </c>
-      <c r="H6" s="39">
+      <c r="H6" s="30">
         <v>22870</v>
       </c>
-      <c r="I6" s="40">
+      <c r="I6" s="31">
         <v>1478000</v>
       </c>
-      <c r="J6" s="39">
+      <c r="J6" s="30">
         <v>591450</v>
       </c>
-      <c r="K6" s="39">
+      <c r="K6" s="30">
         <v>34000</v>
       </c>
-      <c r="L6" s="39">
+      <c r="L6" s="30">
         <v>15060</v>
       </c>
-      <c r="M6" s="39">
+      <c r="M6" s="30">
         <v>181240</v>
       </c>
-      <c r="N6" s="39">
+      <c r="N6" s="30">
         <v>770</v>
       </c>
-      <c r="O6" s="39">
+      <c r="O6" s="30">
         <v>180400</v>
       </c>
-      <c r="P6" s="39">
+      <c r="P6" s="30">
         <v>14390</v>
       </c>
-      <c r="Q6" s="40">
+      <c r="Q6" s="31">
         <v>1017300</v>
       </c>
     </row>
@@ -1619,32 +1613,32 @@
     <row r="22" spans="1:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="1:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="24" spans="1:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="38"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
     </row>
     <row r="25" spans="1:17" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="31"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
+      <c r="A25" s="36"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
       <c r="L25" s="15"/>
@@ -1653,15 +1647,15 @@
       <c r="O25" s="24"/>
     </row>
     <row r="26" spans="1:17" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="32"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
       <c r="J26" s="16"/>
       <c r="K26" s="16"/>
       <c r="L26" s="16"/>
@@ -1670,15 +1664,15 @@
       <c r="O26" s="24"/>
     </row>
     <row r="27" spans="1:17" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="32"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="37"/>
       <c r="J27" s="16"/>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>
@@ -1687,15 +1681,15 @@
       <c r="O27" s="24"/>
     </row>
     <row r="28" spans="1:17" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
+      <c r="A28" s="38"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
       <c r="J28" s="16"/>
       <c r="K28" s="16"/>
       <c r="L28" s="16"/>
@@ -1704,15 +1698,15 @@
       <c r="O28" s="24"/>
     </row>
     <row r="29" spans="1:17" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="31"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
+      <c r="A29" s="36"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="36"/>
       <c r="J29" s="15"/>
       <c r="K29" s="15"/>
       <c r="L29" s="15"/>
@@ -1721,55 +1715,55 @@
       <c r="O29" s="24"/>
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="33"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
-      <c r="O30" s="33"/>
+      <c r="A30" s="39"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="39"/>
     </row>
     <row r="31" spans="1:17" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="34"/>
+      <c r="A31" s="40"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40"/>
+      <c r="L31" s="40"/>
+      <c r="M31" s="40"/>
+      <c r="N31" s="40"/>
+      <c r="O31" s="40"/>
     </row>
     <row r="32" spans="1:17" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="30"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
+      <c r="A32" s="38"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="38"/>
+      <c r="M32" s="38"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="38"/>
       <c r="P32" s="26"/>
     </row>
     <row r="33" spans="1:15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1790,15 +1784,15 @@
       <c r="O33" s="18"/>
     </row>
     <row r="34" spans="1:15" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="31"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
+      <c r="A34" s="36"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
       <c r="J34" s="15"/>
       <c r="K34" s="15"/>
       <c r="L34" s="15"/>
@@ -1808,11 +1802,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="J1:Q1"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A26:I26"/>
     <mergeCell ref="A32:O32"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A27:I27"/>
@@ -1820,6 +1809,11 @@
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A30:O30"/>
     <mergeCell ref="A31:O31"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A26:I26"/>
   </mergeCells>
   <pageMargins left="0.39370078740157499" right="0.47244094488188998" top="0.98425196850393704" bottom="0.98425196850393704" header="0.47244094488188998" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="52" orientation="landscape"/>
